--- a/data/trans_orig/IP1018-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Estudios-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411338</t>
+          <t>411353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471728</t>
+          <t>471236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476466</t>
+          <t>476467</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885485</t>
+          <t>885837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891841</t>
+          <t>891901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676287</t>
+          <t>676184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716694</t>
+          <t>716565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721450</t>
+          <t>721974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395860</t>
+          <t>1395710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401754</t>
+          <t>1401751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56410</t>
+          <t>56494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124763</t>
+          <t>124470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468480</t>
+          <t>467899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481715</t>
+          <t>483137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953771</t>
+          <t>953667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960387</t>
+          <t>960422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698947</t>
+          <t>698850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703789</t>
+          <t>703788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739343</t>
+          <t>739256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1441262</t>
+          <t>1440989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448037</t>
+          <t>1448022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1018-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4964</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4734</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4824</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5755</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475068</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472027</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476467</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>414713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>411353</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>411263</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475068</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471236</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476467</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1342</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885837</t>
+          <t>885593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891901</t>
+          <t>891834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4837</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4869</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5409</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>720051</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>716593</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721450</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679647</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>676184</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>676152</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>720051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716565</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395710</t>
+          <t>1395647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401751</t>
+          <t>1401792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2438,47 +2438,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2781,47 +2781,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3124,47 +3124,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3467,47 +3467,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2944</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58795</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56494</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56360</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>187</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>125049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5621</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1242</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4391</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5598</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>487059</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>483114</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>471048</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>467899</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>468484</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487059</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>483137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1405</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953667</t>
+          <t>953774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960422</t>
+          <t>959944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4727,47 +4727,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,74 +4957,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6377</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5521</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5588</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>743168</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738467</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>702547</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698850</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>703788</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698848</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>703789</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>743168</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739256</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1440989</t>
+          <t>1441344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448022</t>
+          <t>1447991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
